--- a/reports/devops-juniors-israel-2026-W24.xlsx
+++ b/reports/devops-juniors-israel-2026-W24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="362">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-08T11:18:12</t>
+    <t xml:space="preserve">2026-06-09T10:02:11</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -163,132 +163,144 @@
     <t xml:space="preserve">2026-05-15</t>
   </si>
   <si>
-    <t xml:space="preserve">‫System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRS RADA Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-cato-networks-4398801612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iFOR FINTECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4423356724</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-05</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRS RADA Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-cato-networks-4398801612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iFOR FINTECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
     <t xml:space="preserve">Transmitsecurity</t>
   </si>
   <si>
@@ -307,6 +319,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
   </si>
   <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Support Specialist - Temporary position</t>
   </si>
   <si>
@@ -316,7 +343,13 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
   </si>
   <si>
-    <t xml:space="preserve">Support Engineer</t>
+    <t xml:space="preserve">Bria AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
   </si>
   <si>
     <t xml:space="preserve">Level</t>
@@ -334,21 +367,33 @@
     <t xml:space="preserve">2026-06-07</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aristocrat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-aristocrat-4413900417</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Administrator</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-codevalue-4421843930</t>
-  </si>
-  <si>
     <t xml:space="preserve">Menora Mivtachim Group</t>
   </si>
   <si>
@@ -361,444 +406,540 @@
     <t xml:space="preserve">2026-05-19</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7988127&amp;gh_jid=7988127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allied Worldwide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
   </si>
   <si>
     <t xml:space="preserve">Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4425582424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qb Systems ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-20</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Desktop Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zensar Technologies</t>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strategy Analyst Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer IM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desktop Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sharp Brains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-technician-at-sharp-brains-4421919630</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intezer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-intezer-4417050672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brazil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GlassesUSA.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-glassesusa-com-4400413150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpotNet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoham, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spotnet-4421974444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support – Power Quality Meters &amp; Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elspec Engineering ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-%E2%80%93-power-quality-meters-software-at-elspec-engineering-ltd-4413397801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beth-El Industries Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support &amp; System Administrator (Defense)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recruitricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-system-administrator-defense-at-recruitricks-4425177814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk - 239819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician - junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excis Compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-gness-4425230824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist (Part time )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Service Specialist - Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-service-specialist-tier-1-at-solaredge-technologies-4408365748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
   </si>
   <si>
     <t xml:space="preserve">Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allied Worldwide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-riverside-4409620033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papaya Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-papaya-global-4422929229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strategy Analyst Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT Support Technician-Temporary 10 Months</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-support-technician-temporary-10-months-at-augury-4418665913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412563583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desktop Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sharp Brains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-technician-at-sharp-brains-4421919630</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (IT Support Specialist)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-it-support-specialist-at-unilink-ltd-4422886760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Algorithm System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/algorithm-system-engineer-at-elbit-systems-israel-4412906510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brazil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beth-El Industries Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support &amp; System Administrator (Defense)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">recruitricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-system-administrator-defense-at-recruitricks-4425177814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician - junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excis Compliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoham, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk - 239819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist (Part time )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-intel-4424065569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425087450</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer- 2084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-2084-at-tsg-4413409224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-south-apac-sea-anz-ind-subcont-4417601752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-4419979615</t>
   </si>
   <si>
     <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
   </si>
   <si>
+    <t xml:space="preserve">Help Desk Support Specialist (35788)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-35788-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4425488489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
+  </si>
+  <si>
     <t xml:space="preserve">Information Technology Help Desk</t>
   </si>
   <si>
@@ -823,22 +964,10 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9C%D7%97%D7%91%D7%A8%D7%AA-%D7%91%D7%99%D7%98%D7%95%D7%97-%D7%A6%D7%95%D7%9E%D7%97%D7%AA-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%93%D7%A8%D7%95%D7%A9-%D7%94-helpdesk-at-taldor-4425008649</t>
   </si>
   <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4425470752</t>
   </si>
   <si>
     <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
@@ -847,6 +976,24 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4420118096</t>
   </si>
   <si>
+    <t xml:space="preserve">Fireberry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fireberry-4415491964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-south-apac-sea-anz-ind-subcont-4390170199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-4417759260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
+  </si>
+  <si>
     <t xml:space="preserve">Skill</t>
   </si>
   <si>
@@ -862,6 +1009,9 @@
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
@@ -874,13 +1024,13 @@
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
     <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
     <t xml:space="preserve">Linux</t>
@@ -902,12 +1052,6 @@
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
     <t xml:space="preserve">CI/CD</t>
@@ -1080,7 +1224,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>54</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
@@ -1088,7 +1232,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -1096,7 +1240,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -1104,7 +1248,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>209</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10">
@@ -1186,7 +1330,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22">
@@ -1194,7 +1338,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -1202,7 +1346,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -1228,7 +1372,7 @@
         <v>30</v>
       </c>
       <c r="B27" s="3">
-        <v>45</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28">
@@ -1236,7 +1380,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
@@ -1256,7 +1400,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1344,10 +1488,10 @@
         <v>51</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F3" s="3">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>52</v>
@@ -1591,31 +1735,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>91</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="3">
+        <v>51</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="3">
-        <v>47</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="12">
@@ -1629,7 +1773,7 @@
         <v>95</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>25</v>
@@ -1638,16 +1782,16 @@
         <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -1655,31 +1799,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="3">
+        <v>47</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="3">
-        <v>44</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="H13" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14">
@@ -1687,31 +1831,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>105</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -1722,28 +1866,28 @@
         <v>106</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="3">
+        <v>44</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" s="3">
-        <v>36</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -1751,31 +1895,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>77</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
@@ -1783,31 +1927,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="3">
+        <v>40</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17" s="3">
-        <v>28</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="18">
@@ -1815,31 +1959,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
@@ -1847,31 +1991,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20">
@@ -1879,31 +2023,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>48</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21">
@@ -1911,31 +2055,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>135</v>
+        <v>44</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22">
@@ -1943,31 +2087,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>48</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23">
@@ -1975,31 +2119,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>63</v>
+        <v>139</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24">
@@ -2007,19 +2151,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>61</v>
+        <v>143</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>145</v>
@@ -2028,10 +2172,10 @@
         <v>30</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>149</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25">
@@ -2039,31 +2183,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F25" s="3">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>155</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26">
@@ -2071,31 +2215,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>60</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -2134,7 +2278,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="31" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2148,7 +2292,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2163,22 +2307,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2">
@@ -2201,7 +2345,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
@@ -2213,7 +2357,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -2227,16 +2371,16 @@
         <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E3" s="3">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>30</v>
@@ -2248,7 +2392,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -2271,7 +2415,7 @@
         <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>30</v>
@@ -2283,7 +2427,7 @@
         <v>60</v>
       </c>
       <c r="K4" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -2306,7 +2450,7 @@
         <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>30</v>
@@ -2318,7 +2462,7 @@
         <v>66</v>
       </c>
       <c r="K5" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -2341,7 +2485,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>30</v>
@@ -2353,7 +2497,7 @@
         <v>60</v>
       </c>
       <c r="K6" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -2376,7 +2520,7 @@
         <v>73</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>30</v>
@@ -2388,7 +2532,7 @@
         <v>48</v>
       </c>
       <c r="K7" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -2411,7 +2555,7 @@
         <v>78</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>30</v>
@@ -2423,7 +2567,7 @@
         <v>66</v>
       </c>
       <c r="K8" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -2446,7 +2590,7 @@
         <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>30</v>
@@ -2458,7 +2602,7 @@
         <v>60</v>
       </c>
       <c r="K9" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -2481,7 +2625,7 @@
         <v>88</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>30</v>
@@ -2493,42 +2637,42 @@
         <v>90</v>
       </c>
       <c r="K10" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>91</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="3">
+        <v>51</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="3">
-        <v>47</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="K11" s="3">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -2539,7 +2683,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>25</v>
@@ -2548,92 +2692,92 @@
         <v>47</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="K12" s="3">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="3">
+        <v>47</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="3">
-        <v>44</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="G13" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="K13" s="3">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>105</v>
+        <v>48</v>
       </c>
       <c r="K14" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -2641,731 +2785,731 @@
         <v>106</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="3">
+        <v>44</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="3">
-        <v>36</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="K15" s="3">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>77</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="K16" s="3">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="3">
+        <v>40</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="3">
-        <v>28</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="K17" s="3">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="K18" s="3">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="K19" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E20" s="3">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="K20" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>135</v>
+        <v>44</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="K21" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="K22" s="3">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>63</v>
+        <v>139</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="K23" s="3">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>61</v>
+        <v>143</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>145</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>149</v>
+        <v>90</v>
       </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E25" s="3">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>155</v>
+        <v>48</v>
       </c>
       <c r="K25" s="3">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="K26" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>166</v>
+        <v>117</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="3">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="K27" s="3">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="K28" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>175</v>
+        <v>49</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="3">
+        <v>23</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29" s="3">
-        <v>13</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="J29" s="3" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="K29" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="3">
+        <v>20</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E30" s="3">
-        <v>13</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="J30" s="3" t="s">
-        <v>149</v>
+        <v>48</v>
       </c>
       <c r="K30" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" s="3">
+        <v>17</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="J31" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="3">
-        <v>13</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="K31" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" s="3">
+        <v>16</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="3">
-        <v>13</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="J32" s="3" t="s">
-        <v>191</v>
+        <v>142</v>
       </c>
       <c r="K32" s="3">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>82</v>
+        <v>190</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E33" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="K33" s="3">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="D34" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E34" s="3">
+        <v>13</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="G34" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34" s="3">
-        <v>10</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>198</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>60</v>
       </c>
       <c r="K34" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E35" s="3">
+        <v>13</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="J35" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E35" s="3">
-        <v>10</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="K35" s="3">
         <v>15</v>
@@ -3373,69 +3517,69 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E36" s="3">
+        <v>13</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E36" s="3">
-        <v>10</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="K36" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>61</v>
+        <v>203</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>60</v>
+        <v>199</v>
       </c>
       <c r="K37" s="3">
         <v>15</v>
@@ -3443,45 +3587,45 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="D38" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="3">
+        <v>13</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="G38" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E38" s="3">
-        <v>8</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="J38" s="3" t="s">
-        <v>60</v>
+        <v>202</v>
       </c>
       <c r="K38" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>77</v>
@@ -3490,468 +3634,468 @@
         <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>216</v>
+        <v>186</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="K39" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E40" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K40" s="3">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" s="3">
+        <v>10</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E41" s="3">
-        <v>6</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>226</v>
-      </c>
       <c r="J41" s="3" t="s">
-        <v>227</v>
+        <v>60</v>
       </c>
       <c r="K41" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>228</v>
+        <v>49</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E42" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="K42" s="3">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>191</v>
+        <v>229</v>
       </c>
       <c r="K43" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>132</v>
+        <v>231</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E44" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="K44" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>237</v>
+        <v>61</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>239</v>
+        <v>63</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E45" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>60</v>
       </c>
       <c r="K45" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>241</v>
+        <v>75</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="K46" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>63</v>
+        <v>242</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E47" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>248</v>
+        <v>199</v>
       </c>
       <c r="K47" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E48" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>206</v>
+        <v>60</v>
       </c>
       <c r="K48" s="3">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>81</v>
+        <v>250</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E49" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F49" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>255</v>
-      </c>
       <c r="J49" s="3" t="s">
-        <v>155</v>
+        <v>202</v>
       </c>
       <c r="K49" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>257</v>
+        <v>148</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>63</v>
+        <v>149</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>30</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>149</v>
+        <v>202</v>
       </c>
       <c r="K50" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>43</v>
+        <v>256</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E51" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>60</v>
+        <v>167</v>
       </c>
       <c r="K51" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E52" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>263</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>30</v>
@@ -3960,33 +4104,33 @@
         <v>264</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>191</v>
+        <v>265</v>
       </c>
       <c r="K52" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>117</v>
+        <v>237</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E53" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>30</v>
@@ -3995,10 +4139,10 @@
         <v>268</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="K53" s="3">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54">
@@ -4009,70 +4153,733 @@
         <v>270</v>
       </c>
       <c r="C54" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E54" s="3">
+        <v>6</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I54" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E54" s="3">
-        <v>3</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>273</v>
-      </c>
       <c r="J54" s="3" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="K54" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E55" s="3">
+        <v>6</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I55" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="J55" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="K55" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E55" s="3">
+      <c r="B56" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E56" s="3">
+        <v>6</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K56" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E57" s="3">
+        <v>6</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="K57" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E58" s="3">
+        <v>6</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="K58" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E59" s="3">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="K59" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="K60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E61" s="3">
+        <v>4</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K61" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E62" s="3">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="K62" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E63" s="3">
+        <v>4</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="K63" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E64" s="3">
         <v>3</v>
       </c>
-      <c r="F55" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="K55" s="3">
-        <v>4</v>
+      <c r="F64" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K64" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E65" s="3">
+        <v>3</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="K66" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E67" s="3">
+        <v>3</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="K67" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E68" s="3">
+        <v>3</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K68" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E69" s="3">
+        <v>3</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" s="3">
+        <v>3</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="K70" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E71" s="3">
+        <v>3</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K71" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="K72" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E73" s="3">
+        <v>3</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="K73" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E74" s="3">
+        <v>0</v>
+      </c>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="K74" s="3">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K55"/>
+  <autoFilter ref="A1:K74"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4128,6 +4935,25 @@
     <hyperlink ref="I53" r:id="rId52"/>
     <hyperlink ref="I54" r:id="rId53"/>
     <hyperlink ref="I55" r:id="rId54"/>
+    <hyperlink ref="I56" r:id="rId55"/>
+    <hyperlink ref="I57" r:id="rId56"/>
+    <hyperlink ref="I58" r:id="rId57"/>
+    <hyperlink ref="I59" r:id="rId58"/>
+    <hyperlink ref="I60" r:id="rId59"/>
+    <hyperlink ref="I61" r:id="rId60"/>
+    <hyperlink ref="I62" r:id="rId61"/>
+    <hyperlink ref="I63" r:id="rId62"/>
+    <hyperlink ref="I64" r:id="rId63"/>
+    <hyperlink ref="I65" r:id="rId64"/>
+    <hyperlink ref="I66" r:id="rId65"/>
+    <hyperlink ref="I67" r:id="rId66"/>
+    <hyperlink ref="I68" r:id="rId67"/>
+    <hyperlink ref="I69" r:id="rId68"/>
+    <hyperlink ref="I70" r:id="rId69"/>
+    <hyperlink ref="I71" r:id="rId70"/>
+    <hyperlink ref="I72" r:id="rId71"/>
+    <hyperlink ref="I73" r:id="rId72"/>
+    <hyperlink ref="I74" r:id="rId73"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4135,11 +4961,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="49" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="59" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -4158,10 +4984,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -4172,99 +4998,99 @@
         <v>61</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>174</v>
+        <v>137</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>177</v>
+        <v>75</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>178</v>
+        <v>236</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>180</v>
+        <v>238</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>181</v>
+        <v>239</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
@@ -4273,63 +5099,86 @@
         <v>6</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>216</v>
+        <v>254</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>217</v>
+        <v>271</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>235</v>
+        <v>287</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="3">
+        <v>4</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="3">
-        <v>6</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>256</v>
+        <v>302</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>257</v>
+        <v>152</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>259</v>
+        <v>303</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>149</v>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G9"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -4338,6 +5187,7 @@
     <hyperlink ref="F6" r:id="rId5"/>
     <hyperlink ref="F7" r:id="rId6"/>
     <hyperlink ref="F8" r:id="rId7"/>
+    <hyperlink ref="F9" r:id="rId8"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4352,178 +5202,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>277</v>
+        <v>326</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>278</v>
+        <v>327</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>279</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>252</v>
+        <v>285</v>
       </c>
       <c r="B2" s="3">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>280</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>267</v>
+        <v>314</v>
       </c>
       <c r="B3" s="3">
         <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>281</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>282</v>
+        <v>195</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>283</v>
+        <v>331</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>284</v>
+        <v>332</v>
       </c>
       <c r="B5" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>285</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>263</v>
+        <v>334</v>
       </c>
       <c r="B6" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>286</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>287</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>173</v>
+        <v>310</v>
       </c>
       <c r="B8" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>288</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>290</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>291</v>
+        <v>339</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>292</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>272</v>
+        <v>341</v>
       </c>
       <c r="B11" s="3">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>293</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B12" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>295</v>
+        <v>343</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>296</v>
+        <v>344</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>297</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>298</v>
+        <v>346</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>299</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>300</v>
+        <v>348</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>301</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>302</v>
+        <v>350</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>303</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -4543,10 +5393,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>304</v>
+        <v>352</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>305</v>
+        <v>353</v>
       </c>
     </row>
     <row r="2">
@@ -4554,10 +5404,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>306</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3">
@@ -4565,10 +5415,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>307</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4">
@@ -4576,10 +5426,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>308</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5">
@@ -4590,7 +5440,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>309</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -4611,13 +5461,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>310</v>
+        <v>358</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>311</v>
+        <v>359</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>312</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2">
@@ -4625,10 +5475,10 @@
         <v>31</v>
       </c>
       <c r="B2" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>313</v>
+        <v>361</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4637,10 +5487,10 @@
         <v>30</v>
       </c>
       <c r="B3" s="3">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>313</v>
+        <v>361</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -4652,7 +5502,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>313</v>
+        <v>361</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W24.xlsx
+++ b/reports/devops-juniors-israel-2026-W24.xlsx
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-09T10:02:11</t>
+    <t xml:space="preserve">2026-06-10T10:20:30</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -103,6 +103,9 @@
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+  </si>
+  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -112,994 +115,991 @@
     <t xml:space="preserve">greenhouse</t>
   </si>
   <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bucket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack you'll work with</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apply URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Seen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jfrog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRS RADA Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fortinet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Networking, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fortinet-4393535304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iFOR FINTECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bria AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA Engineer - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sojo Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/qa-engineer-student-position-at-sojo-industries-4423100988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7988127&amp;gh_jid=7988127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4405103757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4425582424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qb Systems ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papaya Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-papaya-global-4422929229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk &amp; IT Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-it-administrator-at-mize-4425999700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beit Shemesh, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-at-nebius-4425229985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux Software Embedded Engineer (Junior position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDA Space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-software-embedded-engineer-junior-position-at-mda-space-4422723139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strategy Analyst Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT Support Technician-Temporary 10 Months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Augury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-support-technician-temporary-10-months-at-augury-4418665913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer IM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (IT Support Specialist)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-it-support-specialist-at-unilink-ltd-4426750419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intezer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-intezer-4417050672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brazil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beth-El Industries Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support &amp; System Administrator (Defense)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recruitricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-system-administrator-defense-at-recruitricks-4425177814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk - 239819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician - junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4422293340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excis Compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoham, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist (Part time )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragontail Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-agent-at-dragontail-systems-4422278367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Service Specialist - Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-service-specialist-tier-1-at-solaredge-technologies-4408365748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer- 2084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-2084-at-tsg-4413409224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-4419979615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Specialist (35788)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-35788-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4425488489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4425470752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Tier 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yavne, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-at-gness-4426023923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unframe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-unframe-4425465742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fireberry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fireberry-4415491964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (10156)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bynet Data Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-10156-at-bynet-data-communications-4422796719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allied Worldwide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support – Power Quality Meters &amp; Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elspec Engineering ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-%E2%80%93-power-quality-meters-software-at-elspec-engineering-ltd-4413397801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4420118096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pivot path advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error</t>
+  </si>
+  <si>
     <t xml:space="preserve">remoteok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bucket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack you'll work with</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apply URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Seen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jfrog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7563041&amp;gh_jid=7563041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyager Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRS RADA Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-cato-networks-4398801612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iFOR FINTECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4423356724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bria AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Docker, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-support-engineer-level-1132895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aristocrat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-aristocrat-4413900417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7988127&amp;gh_jid=7988127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allied Worldwide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4425582424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strategy Analyst Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer IM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desktop Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sharp Brains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-technician-at-sharp-brains-4421919630</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intezer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-intezer-4417050672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brazil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GlassesUSA.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-glassesusa-com-4400413150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpotNet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoham, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spotnet-4421974444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support – Power Quality Meters &amp; Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elspec Engineering ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-%E2%80%93-power-quality-meters-software-at-elspec-engineering-ltd-4413397801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beth-El Industries Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support &amp; System Administrator (Defense)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">recruitricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-system-administrator-defense-at-recruitricks-4425177814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk - 239819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician - junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excis Compliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-gness-4425230824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist (Part time )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Service Specialist - Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-service-specialist-tier-1-at-solaredge-technologies-4408365748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer- 2084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-2084-at-tsg-4413409224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-south-apac-sea-anz-ind-subcont-4417601752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-4419979615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Specialist (35788)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-35788-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4425488489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">לחברת ביטוח צומחת במרכז דרוש/ה HELPDESK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taldor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9C%D7%97%D7%91%D7%A8%D7%AA-%D7%91%D7%99%D7%98%D7%95%D7%97-%D7%A6%D7%95%D7%9E%D7%97%D7%AA-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%93%D7%A8%D7%95%D7%A9-%D7%94-helpdesk-at-taldor-4425008649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4425470752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4420118096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fireberry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fireberry-4415491964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-south-apac-sea-anz-ind-subcont-4390170199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-4417759260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pivot path advice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
   </si>
 </sst>
 </file>
@@ -1224,7 +1224,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -1232,7 +1232,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -1248,7 +1248,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>217</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10">
@@ -1330,7 +1330,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22">
@@ -1338,7 +1338,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -1346,7 +1346,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1358,29 +1358,29 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
+      <c r="A25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A26" s="3"/>
       <c r="B26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="3">
-        <v>62</v>
-      </c>
+      <c r="B27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>10</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29">
@@ -1388,7 +1388,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1465,7 +1465,7 @@
         <v>46</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>47</v>
@@ -1488,16 +1488,16 @@
         <v>51</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F3" s="3">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>52</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>53</v>
@@ -1520,22 +1520,22 @@
         <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" s="3">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>58</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
@@ -1543,31 +1543,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="3">
+        <v>54</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="3">
-        <v>74</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -1575,31 +1575,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="3">
+        <v>52</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="3">
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="7">
@@ -1613,22 +1613,22 @@
         <v>72</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>48</v>
@@ -1639,31 +1639,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -1671,31 +1671,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F9" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -1703,31 +1703,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F10" s="3">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11">
@@ -1735,31 +1735,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F11" s="3">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -1767,28 +1767,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>48</v>
@@ -1799,31 +1799,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F13" s="3">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14">
@@ -1831,31 +1831,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14" s="3">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>48</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15">
@@ -1863,31 +1863,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>48</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -1895,31 +1895,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>49</v>
+        <v>114</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>54</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17">
@@ -1927,31 +1927,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18">
@@ -1959,31 +1959,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19">
@@ -1991,31 +1991,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20">
@@ -2023,31 +2023,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="E20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="3">
         <v>26</v>
       </c>
-      <c r="F20" s="3">
-        <v>32</v>
-      </c>
       <c r="G20" s="3" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>129</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21">
@@ -2055,31 +2055,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>45</v>
+        <v>138</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22">
@@ -2087,31 +2087,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>134</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>132</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
@@ -2119,31 +2119,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24">
@@ -2151,31 +2151,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25">
@@ -2183,31 +2183,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>147</v>
+        <v>71</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>149</v>
+        <v>62</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>48</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26">
@@ -2215,31 +2215,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>153</v>
+        <v>57</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -2278,7 +2278,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2292,7 +2292,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2307,22 +2307,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2">
@@ -2345,10 +2345,10 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>47</v>
@@ -2357,7 +2357,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -2371,19 +2371,19 @@
         <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3" s="3">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>53</v>
@@ -2392,7 +2392,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -2406,98 +2406,98 @@
         <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4" s="3">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="K4" s="3">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="3">
+        <v>54</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="3">
-        <v>74</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="K5" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="3">
+        <v>52</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="3">
+      <c r="G6" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="K6" s="3">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -2508,693 +2508,693 @@
         <v>72</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K7" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E8" s="3">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="K8" s="3">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E9" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="K9" s="3">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="3">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K10" s="3">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E11" s="3">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K11" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" s="3">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>48</v>
       </c>
       <c r="K12" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E13" s="3">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="K13" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E14" s="3">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="K14" s="3">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>48</v>
+        <v>113</v>
       </c>
       <c r="K15" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>49</v>
+        <v>114</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>54</v>
+        <v>113</v>
       </c>
       <c r="K16" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="K17" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="K18" s="3">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="K19" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="D20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="3">
         <v>26</v>
       </c>
-      <c r="E20" s="3">
-        <v>32</v>
-      </c>
       <c r="F20" s="3" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>129</v>
+        <v>48</v>
       </c>
       <c r="K20" s="3">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>45</v>
+        <v>138</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="K21" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>134</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="3">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>132</v>
+        <v>48</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="K23" s="3">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="K24" s="3">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>147</v>
+        <v>71</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>149</v>
+        <v>62</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>48</v>
+        <v>155</v>
       </c>
       <c r="K25" s="3">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>153</v>
+        <v>57</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="K26" s="3">
         <v>0</v>
@@ -3202,188 +3202,188 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>117</v>
+        <v>166</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>48</v>
+        <v>105</v>
       </c>
       <c r="K27" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>75</v>
+        <v>171</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>77</v>
+        <v>173</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E28" s="3">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>167</v>
+        <v>105</v>
       </c>
       <c r="K28" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>49</v>
+        <v>176</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E29" s="3">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="K29" s="3">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="K30" s="3">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>180</v>
+        <v>126</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E31" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>183</v>
+        <v>65</v>
       </c>
       <c r="K31" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>26</v>
@@ -3392,68 +3392,68 @@
         <v>16</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="K32" s="3">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E33" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="K33" s="3">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>27</v>
@@ -3462,19 +3462,19 @@
         <v>13</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>60</v>
+        <v>201</v>
       </c>
       <c r="K34" s="3">
         <v>16</v>
@@ -3482,83 +3482,83 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E35" s="3">
         <v>13</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="K35" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E36" s="3">
         <v>13</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>202</v>
+        <v>105</v>
       </c>
       <c r="K36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
@@ -3567,138 +3567,138 @@
         <v>13</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>199</v>
+        <v>91</v>
       </c>
       <c r="K37" s="3">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E38" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>202</v>
+        <v>132</v>
       </c>
       <c r="K38" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>77</v>
+        <v>218</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>186</v>
+        <v>219</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="K39" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>184</v>
+        <v>60</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E40" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="K40" s="3">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>218</v>
+        <v>71</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>220</v>
+        <v>57</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
@@ -3707,264 +3707,264 @@
         <v>10</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="K41" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>49</v>
+        <v>226</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E42" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="K42" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>229</v>
+        <v>155</v>
       </c>
       <c r="K43" s="3">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>231</v>
+        <v>134</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E44" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>199</v>
+        <v>155</v>
       </c>
       <c r="K44" s="3">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>61</v>
+        <v>238</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>63</v>
+        <v>240</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E45" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>60</v>
+        <v>146</v>
       </c>
       <c r="K45" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>75</v>
+        <v>242</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>132</v>
+        <v>247</v>
       </c>
       <c r="K46" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E47" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>199</v>
+        <v>105</v>
       </c>
       <c r="K47" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>246</v>
+        <v>57</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E48" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>60</v>
+        <v>201</v>
       </c>
       <c r="K48" s="3">
         <v>16</v>
@@ -3972,13 +3972,13 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>77</v>
+        <v>257</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>25</v>
@@ -3987,33 +3987,33 @@
         <v>6</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>202</v>
+        <v>54</v>
       </c>
       <c r="K49" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>148</v>
+        <v>260</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>149</v>
+        <v>57</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
@@ -4022,33 +4022,33 @@
         <v>6</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>202</v>
+        <v>95</v>
       </c>
       <c r="K50" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>258</v>
+        <v>102</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
@@ -4057,33 +4057,33 @@
         <v>6</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>167</v>
+        <v>105</v>
       </c>
       <c r="K51" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>262</v>
+        <v>62</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
@@ -4092,418 +4092,418 @@
         <v>6</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>263</v>
+        <v>229</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>265</v>
+        <v>146</v>
       </c>
       <c r="K52" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>237</v>
+        <v>271</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E53" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>60</v>
+        <v>274</v>
       </c>
       <c r="K53" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>139</v>
+        <v>277</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E54" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="K54" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>63</v>
+        <v>282</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E55" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>251</v>
+        <v>283</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>199</v>
+        <v>54</v>
       </c>
       <c r="K55" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E56" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>54</v>
+        <v>274</v>
       </c>
       <c r="K56" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>212</v>
+        <v>43</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>148</v>
+        <v>270</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>149</v>
+        <v>271</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E57" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>247</v>
+        <v>272</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="K57" s="3">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>280</v>
+        <v>137</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>87</v>
+        <v>126</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E58" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>247</v>
+        <v>272</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>167</v>
+        <v>113</v>
       </c>
       <c r="K58" s="3">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>284</v>
+        <v>83</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E59" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>229</v>
+        <v>201</v>
       </c>
       <c r="K59" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>289</v>
+        <v>88</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E60" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="K60" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>292</v>
+        <v>119</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>294</v>
+        <v>102</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E61" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="K61" s="3">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>63</v>
+        <v>302</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E62" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>229</v>
+        <v>105</v>
       </c>
       <c r="K62" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>282</v>
+        <v>76</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E63" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>229</v>
+        <v>105</v>
       </c>
       <c r="K63" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>284</v>
+        <v>83</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>25</v>
@@ -4512,374 +4512,191 @@
         <v>3</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="K64" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>152</v>
+        <v>195</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>149</v>
+        <v>184</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E65" s="3">
-        <v>3</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>285</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>132</v>
+        <v>201</v>
       </c>
       <c r="K65" s="3">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>51</v>
+        <v>126</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E66" s="3">
-        <v>3</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>306</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
-        <v>161</v>
+        <v>312</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>167</v>
+        <v>105</v>
       </c>
       <c r="K66" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E67" s="3">
-        <v>3</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>310</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>161</v>
+        <v>312</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>199</v>
+        <v>70</v>
       </c>
       <c r="K67" s="3">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E68" s="3">
+        <v>0</v>
+      </c>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E68" s="3">
-        <v>3</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="H68" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>116</v>
+        <v>201</v>
       </c>
       <c r="K68" s="3">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>169</v>
+        <v>322</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E69" s="3">
-        <v>3</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>285</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
-        <v>161</v>
+        <v>312</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="K69" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E70" s="3">
-        <v>3</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="K70" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E71" s="3">
-        <v>3</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="J71" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="K71" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E72" s="3">
-        <v>3</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K72" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E73" s="3">
-        <v>3</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="J73" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K73" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E74" s="3">
-        <v>0</v>
-      </c>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="J74" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K74" s="3">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K74"/>
+  <autoFilter ref="A1:K69"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4949,11 +4766,6 @@
     <hyperlink ref="I67" r:id="rId66"/>
     <hyperlink ref="I68" r:id="rId67"/>
     <hyperlink ref="I69" r:id="rId68"/>
-    <hyperlink ref="I70" r:id="rId69"/>
-    <hyperlink ref="I71" r:id="rId70"/>
-    <hyperlink ref="I72" r:id="rId71"/>
-    <hyperlink ref="I73" r:id="rId72"/>
-    <hyperlink ref="I74" r:id="rId73"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4961,9 +4773,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="1" max="1" width="52" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -4984,10 +4796,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -4995,171 +4807,171 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D2" s="3">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>75</v>
+        <v>171</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>236</v>
+        <v>172</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D5" s="3">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>238</v>
+        <v>174</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>239</v>
+        <v>175</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>269</v>
+        <v>206</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>270</v>
+        <v>207</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>254</v>
+        <v>208</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>271</v>
+        <v>209</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>287</v>
+        <v>248</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>288</v>
+        <v>249</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>290</v>
+        <v>233</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>291</v>
+        <v>251</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>302</v>
+        <v>262</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>303</v>
+        <v>265</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>75</v>
+        <v>300</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>25</v>
@@ -5168,17 +4980,61 @@
         <v>3</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>132</v>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G11"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -5188,6 +5044,8 @@
     <hyperlink ref="F7" r:id="rId6"/>
     <hyperlink ref="F8" r:id="rId7"/>
     <hyperlink ref="F9" r:id="rId8"/>
+    <hyperlink ref="F10" r:id="rId9"/>
+    <hyperlink ref="F11" r:id="rId10"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5202,43 +5060,43 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="B2" s="3">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="B3" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>195</v>
+        <v>330</v>
       </c>
       <c r="B4" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>331</v>
@@ -5246,43 +5104,43 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B5" s="3">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>332</v>
-      </c>
-      <c r="B5" s="3">
-        <v>20</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B6" s="3">
+        <v>14</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>334</v>
-      </c>
-      <c r="B6" s="3">
-        <v>19</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>337</v>
@@ -5290,10 +5148,10 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="B9" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>338</v>
@@ -5301,79 +5159,79 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B10" s="3">
+        <v>12</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>339</v>
-      </c>
-      <c r="B10" s="3">
-        <v>13</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>341</v>
+        <v>296</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>306</v>
+        <v>341</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B13" s="3">
+        <v>6</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>344</v>
-      </c>
-      <c r="B13" s="3">
-        <v>8</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="B14" s="3">
+        <v>5</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>346</v>
-      </c>
-      <c r="B14" s="3">
-        <v>7</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B15" s="3">
+        <v>4</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="B15" s="3">
-        <v>6</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B16" s="3">
+        <v>3</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>350</v>
-      </c>
-      <c r="B16" s="3">
-        <v>4</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -5393,10 +5251,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="2">
@@ -5404,10 +5262,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3">
@@ -5415,10 +5273,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4">
@@ -5426,10 +5284,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5">
@@ -5440,6 +5298,17 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>357</v>
       </c>
     </row>
@@ -5472,37 +5341,37 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3">
         <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>361</v>
+        <v>312</v>
       </c>
       <c r="D2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>361</v>
+        <v>312</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>32</v>
+        <v>361</v>
       </c>
       <c r="B4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>361</v>
+        <v>312</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W24.xlsx
+++ b/reports/devops-juniors-israel-2026-W24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="359">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-10T10:20:30</t>
+    <t xml:space="preserve">2026-06-11T10:56:37</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -115,6 +115,9 @@
     <t xml:space="preserve">greenhouse</t>
   </si>
   <si>
+    <t xml:space="preserve">remoteok</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rank</t>
   </si>
   <si>
@@ -163,24 +166,42 @@
     <t xml:space="preserve">2026-05-15</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRS RADA Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior IT / Cloud Specialist - 235226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-cloud-specialist-235226-at-experis-israel-4423620429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
   </si>
   <si>
@@ -202,9 +223,6 @@
     <t xml:space="preserve">Fortinet</t>
   </si>
   <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Networking, Virtualization, Troubleshooting</t>
   </si>
   <si>
@@ -214,456 +232,477 @@
     <t xml:space="preserve">2026-05-31</t>
   </si>
   <si>
-    <t xml:space="preserve">Experienced IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iFOR FINTECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
+    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infrastructure &amp; Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Squadron Israel - Hatayeset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-technical-support-specialist-at-the-squadron-israel-hatayeset-4421938671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bria AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-comblack-4425486490</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7988127&amp;gh_jid=7988127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allied Worldwide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-03</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bria AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
   </si>
   <si>
     <t xml:space="preserve">NOC Operator</t>
   </si>
   <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QA Engineer - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sojo Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/qa-engineer-student-position-at-sojo-industries-4423100988</t>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qb Systems ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (10156)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bynet Data Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-10156-at-bynet-data-communications-4422796719</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-10</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7988127&amp;gh_jid=7988127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4405103757</t>
+    <t xml:space="preserve">Linux Software Embedded Engineer (Junior position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDA Space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-software-embedded-engineer-junior-position-at-mda-space-4422723139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strategy Analyst Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT Support Technician-Temporary 10 Months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Augury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-support-technician-temporary-10-months-at-augury-4418665913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Eng.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultra Information Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-eng-at-ultra-information-solutions-4412395476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer IM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-extreme-4426735920</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-extreme-4426743545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (IT Support Specialist)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-it-support-specialist-at-unilink-ltd-4426750419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intezer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-intezer-4417050672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-01</t>
   </si>
   <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4425582424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papaya Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-papaya-global-4422929229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk &amp; IT Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-it-administrator-at-mize-4425999700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beit Shemesh, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-at-nebius-4425229985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux Software Embedded Engineer (Junior position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MDA Space</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-software-embedded-engineer-junior-position-at-mda-space-4422723139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strategy Analyst Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT Support Technician-Temporary 10 Months</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-support-technician-temporary-10-months-at-augury-4418665913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer IM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (IT Support Specialist)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-it-support-specialist-at-unilink-ltd-4426750419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intezer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-intezer-4417050672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
-  </si>
-  <si>
     <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
   </si>
   <si>
@@ -694,105 +733,90 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beth-El Industries Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician - junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support &amp; System Administrator (Defense)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">recruitricks</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
   </si>
   <si>
     <t xml:space="preserve">Networking, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-system-administrator-defense-at-recruitricks-4425177814</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
   </si>
   <si>
     <t xml:space="preserve">Help Desk</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
   </si>
   <si>
+    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excis Compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoham, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4422293340</t>
+  </si>
+  <si>
     <t xml:space="preserve">Help Desk - 239819</t>
   </si>
   <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk Technician - junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4422293340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excis Compliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoham, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Specialist (Part time )</t>
   </si>
   <si>
@@ -814,6 +838,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-agent-at-dragontail-systems-4422278367</t>
   </si>
   <si>
+    <t xml:space="preserve">Technical Support Representative (Full-Time, On-Site | Be’er Sheva – Gav Yam Park)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SITE123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-representative-full-time-on-site-be%E2%80%99er-sheva-%E2%80%93-gav-yam-park-at-site123-4419228442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
     <t xml:space="preserve">Technical Service Specialist - Tier 1</t>
   </si>
   <si>
@@ -847,259 +886,211 @@
     <t xml:space="preserve">UR Tech Jobs</t>
   </si>
   <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
   </si>
   <si>
-    <t xml:space="preserve">System Engineer- 2084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-south-apac-sea-anz-ind-subcont-4423614421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-4419979615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4425470752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4420118096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fireberry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fireberry-4415491964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-south-apac-sea-anz-ind-subcont-4390170199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unframe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-unframe-4425465742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-4417759260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programa Trainee 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universia Argentina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Isidro, San Isidro, Provincia de Buenos Aires, Argentina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-programa-trainee-2026-universia-argentina-1133156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-2084-at-tsg-4413409224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-4419979615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Specialist (35788)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-35788-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4425488489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4425470752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Tier 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yavne, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-at-gness-4426023923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unframe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-unframe-4425465742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fireberry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fireberry-4415491964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (10156)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bynet Data Communications</t>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pivot path advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error</t>
   </si>
   <si>
     <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-10156-at-bynet-data-communications-4422796719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allied Worldwide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support – Power Quality Meters &amp; Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elspec Engineering ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-%E2%80%93-power-quality-meters-software-at-elspec-engineering-ltd-4413397801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4420118096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pivot path advice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remoteok</t>
   </si>
 </sst>
 </file>
@@ -1224,7 +1215,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -1232,7 +1223,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1248,7 +1239,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>227</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10">
@@ -1330,7 +1321,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
@@ -1338,7 +1329,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -1346,7 +1337,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1354,7 +1345,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1380,7 +1371,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29">
@@ -1389,6 +1380,14 @@
       </c>
       <c r="B29" s="3">
         <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1400,8 +1399,8 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="42" customWidth="1"/>
+    <col min="3" max="3" width="33" customWidth="1"/>
+    <col min="4" max="4" width="43" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
@@ -1412,34 +1411,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -1447,13 +1446,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>25</v>
@@ -1462,16 +1461,16 @@
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -1479,31 +1478,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -1511,31 +1510,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F4" s="3">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -1543,31 +1542,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F5" s="3">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
@@ -1575,31 +1574,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -1607,31 +1606,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F7" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8">
@@ -1639,13 +1638,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
@@ -1654,16 +1653,16 @@
         <v>47</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -1671,31 +1670,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F9" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -1703,31 +1702,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10" s="3">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>91</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11">
@@ -1735,31 +1734,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F11" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
@@ -1767,31 +1766,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" s="3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -1799,31 +1798,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14">
@@ -1831,31 +1830,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -1863,31 +1862,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>44</v>
+        <v>113</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>113</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -1895,31 +1894,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>113</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17">
@@ -1927,13 +1926,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
@@ -1942,16 +1941,16 @@
         <v>30</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="18">
@@ -1959,31 +1958,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="3">
+        <v>30</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F18" s="3">
-        <v>28</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19">
@@ -1991,31 +1990,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>51</v>
+        <v>130</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>132</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20">
@@ -2029,25 +2028,25 @@
         <v>134</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>48</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21">
@@ -2055,31 +2054,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22">
@@ -2087,31 +2086,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>96</v>
+        <v>143</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="3">
         <v>26</v>
       </c>
-      <c r="F22" s="3">
-        <v>24</v>
-      </c>
       <c r="G22" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
@@ -2119,31 +2118,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>146</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24">
@@ -2151,31 +2150,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>149</v>
+        <v>99</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>48</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25">
@@ -2183,31 +2182,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>155</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26">
@@ -2215,13 +2214,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>57</v>
+        <v>159</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
@@ -2230,16 +2229,16 @@
         <v>20</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>105</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2278,8 +2277,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2292,48 +2291,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>25</v>
@@ -2342,208 +2341,208 @@
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E3" s="3">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="3">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="K4" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E5" s="3">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="K5" s="3">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E7" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="K7" s="3">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>25</v>
@@ -2552,313 +2551,313 @@
         <v>47</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K8" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E9" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="K9" s="3">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E10" s="3">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>91</v>
+        <v>49</v>
       </c>
       <c r="K10" s="3">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E11" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="K11" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" s="3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K12" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K13" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K14" s="3">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>44</v>
+        <v>113</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>113</v>
+        <v>61</v>
       </c>
       <c r="K15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>113</v>
+        <v>61</v>
       </c>
       <c r="K16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
@@ -2867,92 +2866,92 @@
         <v>30</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="K17" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="3">
+        <v>30</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="3">
-        <v>28</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="K18" s="3">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>129</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>51</v>
+        <v>130</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>132</v>
+        <v>71</v>
       </c>
       <c r="K19" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -2963,217 +2962,217 @@
         <v>134</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E20" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>48</v>
+        <v>107</v>
       </c>
       <c r="K20" s="3">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="K21" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>96</v>
+        <v>143</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="D22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="3">
         <v>26</v>
       </c>
-      <c r="E22" s="3">
-        <v>24</v>
-      </c>
       <c r="F22" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K22" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E23" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>146</v>
+        <v>49</v>
       </c>
       <c r="K23" s="3">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>149</v>
+        <v>99</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>48</v>
+        <v>153</v>
       </c>
       <c r="K24" s="3">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>155</v>
+        <v>107</v>
       </c>
       <c r="K25" s="3">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>57</v>
+        <v>159</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>25</v>
@@ -3182,68 +3181,68 @@
         <v>20</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>105</v>
+        <v>49</v>
       </c>
       <c r="K26" s="3">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" s="3">
         <v>20</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="K27" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>29</v>
@@ -3252,33 +3251,33 @@
         <v>18</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="K28" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>27</v>
@@ -3287,33 +3286,33 @@
         <v>17</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K29" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>184</v>
+        <v>74</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
@@ -3322,68 +3321,68 @@
         <v>17</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K30" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="K31" s="3">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>26</v>
@@ -3392,68 +3391,68 @@
         <v>16</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K32" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>194</v>
+        <v>50</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>195</v>
+        <v>134</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>196</v>
+        <v>135</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E33" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F33" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="J33" s="3" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="K33" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>195</v>
-      </c>
       <c r="C34" s="3" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>27</v>
@@ -3462,57 +3461,57 @@
         <v>13</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>201</v>
+        <v>55</v>
       </c>
       <c r="K34" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E35" s="3">
         <v>13</v>
       </c>
       <c r="F35" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I35" s="3" t="s">
+      <c r="J35" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>201</v>
-      </c>
       <c r="K35" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36">
@@ -3520,45 +3519,45 @@
         <v>206</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E36" s="3">
         <v>13</v>
       </c>
       <c r="F36" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="K36" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>211</v>
+        <v>134</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
@@ -3567,27 +3566,27 @@
         <v>13</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="K37" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>213</v>
@@ -3596,16 +3595,16 @@
         <v>214</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
@@ -3614,10 +3613,10 @@
         <v>215</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>132</v>
+        <v>61</v>
       </c>
       <c r="K38" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3628,63 +3627,63 @@
         <v>217</v>
       </c>
       <c r="C39" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="3">
+        <v>13</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39" s="3">
-        <v>10</v>
-      </c>
-      <c r="F39" s="3" t="s">
+      <c r="G39" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>220</v>
-      </c>
       <c r="J39" s="3" t="s">
-        <v>54</v>
+        <v>172</v>
       </c>
       <c r="K39" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>60</v>
+        <v>209</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C40" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="3">
+        <v>13</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E40" s="3">
-        <v>10</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>219</v>
-      </c>
       <c r="G40" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>222</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>54</v>
+        <v>205</v>
       </c>
       <c r="K40" s="3">
         <v>17</v>
@@ -3692,188 +3691,188 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>223</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F41" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>225</v>
-      </c>
       <c r="J41" s="3" t="s">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="K41" s="3">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>227</v>
-      </c>
       <c r="C42" s="3" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E42" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>229</v>
+        <v>201</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>54</v>
+        <v>228</v>
       </c>
       <c r="K42" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="D43" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" s="3">
+        <v>10</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E43" s="3">
-        <v>6</v>
-      </c>
-      <c r="F43" s="3" t="s">
+      <c r="G43" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I43" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>234</v>
-      </c>
       <c r="J43" s="3" t="s">
-        <v>155</v>
+        <v>55</v>
       </c>
       <c r="K43" s="3">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E44" s="3">
+        <v>10</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E44" s="3">
-        <v>6</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>237</v>
-      </c>
       <c r="J44" s="3" t="s">
-        <v>155</v>
+        <v>55</v>
       </c>
       <c r="K44" s="3">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E45" s="3">
+        <v>10</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I45" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E45" s="3">
-        <v>6</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>241</v>
-      </c>
       <c r="J45" s="3" t="s">
-        <v>146</v>
+        <v>55</v>
       </c>
       <c r="K45" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
@@ -3882,33 +3881,33 @@
         <v>6</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>247</v>
+        <v>55</v>
       </c>
       <c r="K46" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
@@ -3917,33 +3916,33 @@
         <v>6</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>105</v>
+        <v>248</v>
       </c>
       <c r="K47" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>253</v>
+        <v>144</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>57</v>
+        <v>135</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
@@ -3952,33 +3951,33 @@
         <v>6</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>201</v>
+        <v>142</v>
       </c>
       <c r="K48" s="3">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>257</v>
+        <v>64</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>25</v>
@@ -3987,19 +3986,19 @@
         <v>6</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>54</v>
+        <v>205</v>
       </c>
       <c r="K49" s="3">
         <v>17</v>
@@ -4007,13 +4006,13 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>260</v>
+        <v>144</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>57</v>
+        <v>135</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
@@ -4022,33 +4021,33 @@
         <v>6</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>95</v>
+        <v>208</v>
       </c>
       <c r="K50" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>102</v>
+        <v>259</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
@@ -4057,33 +4056,33 @@
         <v>6</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="K51" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>62</v>
+        <v>240</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
@@ -4092,348 +4091,348 @@
         <v>6</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="K52" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>270</v>
+        <v>57</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E53" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>272</v>
+        <v>241</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>274</v>
+        <v>153</v>
       </c>
       <c r="K53" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>277</v>
+        <v>64</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E54" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>278</v>
+        <v>241</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K54" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>282</v>
+        <v>84</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E55" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>54</v>
+        <v>172</v>
       </c>
       <c r="K55" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>57</v>
+        <v>276</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E56" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="K56" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>43</v>
+        <v>279</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>271</v>
+        <v>52</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E57" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>54</v>
+        <v>153</v>
       </c>
       <c r="K57" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>137</v>
+        <v>283</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>126</v>
+        <v>284</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E58" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>113</v>
+        <v>287</v>
       </c>
       <c r="K58" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E59" s="3">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="G59" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I59" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E59" s="3">
-        <v>3</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>293</v>
-      </c>
       <c r="J59" s="3" t="s">
-        <v>201</v>
+        <v>122</v>
       </c>
       <c r="K59" s="3">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E60" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>146</v>
+        <v>61</v>
       </c>
       <c r="K60" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>119</v>
+        <v>282</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E61" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>113</v>
+        <v>287</v>
       </c>
       <c r="K61" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>300</v>
+        <v>44</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>25</v>
@@ -4442,33 +4441,33 @@
         <v>3</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="K62" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>76</v>
+        <v>297</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>25</v>
@@ -4477,33 +4476,33 @@
         <v>3</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>105</v>
+        <v>205</v>
       </c>
       <c r="K63" s="3">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>25</v>
@@ -4512,191 +4511,302 @@
         <v>3</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>54</v>
+        <v>122</v>
       </c>
       <c r="K64" s="3">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>308</v>
+        <v>67</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>195</v>
+        <v>303</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>184</v>
+        <v>64</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E65" s="3">
-        <v>0</v>
-      </c>
-      <c r="F65" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>290</v>
+      </c>
       <c r="G65" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>201</v>
+        <v>55</v>
       </c>
       <c r="K65" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>310</v>
+        <v>82</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>126</v>
+        <v>58</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E66" s="3">
-        <v>0</v>
-      </c>
-      <c r="F66" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>285</v>
+      </c>
       <c r="G66" s="3" t="s">
-        <v>312</v>
+        <v>167</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>105</v>
+        <v>183</v>
       </c>
       <c r="K66" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>314</v>
+        <v>67</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E67" s="3">
-        <v>0</v>
-      </c>
-      <c r="F67" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>285</v>
+      </c>
       <c r="G67" s="3" t="s">
-        <v>312</v>
+        <v>167</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="K67" s="3">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>317</v>
+        <v>44</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>318</v>
+        <v>292</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>319</v>
+        <v>64</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E68" s="3">
-        <v>0</v>
-      </c>
-      <c r="F68" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>285</v>
+      </c>
       <c r="G68" s="3" t="s">
-        <v>312</v>
+        <v>167</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="K68" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>210</v>
+        <v>87</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>322</v>
+        <v>64</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E69" s="3">
+        <v>3</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="K69" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" s="3">
+        <v>3</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="K70" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E71" s="3">
         <v>0</v>
       </c>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="K69" s="3">
-        <v>6</v>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="K71" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E72" s="3">
+        <v>0</v>
+      </c>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K72" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K69"/>
+  <autoFilter ref="A1:K72"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4766,6 +4876,9 @@
     <hyperlink ref="I67" r:id="rId66"/>
     <hyperlink ref="I68" r:id="rId67"/>
     <hyperlink ref="I69" r:id="rId68"/>
+    <hyperlink ref="I70" r:id="rId69"/>
+    <hyperlink ref="I71" r:id="rId70"/>
+    <hyperlink ref="I72" r:id="rId71"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4773,9 +4886,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="52" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="1" max="1" width="53" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -4784,257 +4897,234 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" s="3">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>105</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>156</v>
+        <v>92</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>157</v>
+        <v>93</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>158</v>
+        <v>95</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>159</v>
+        <v>96</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>105</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>167</v>
+        <v>113</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>169</v>
+        <v>114</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>105</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>172</v>
+        <v>116</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>174</v>
+        <v>118</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>175</v>
+        <v>119</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>105</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>206</v>
+        <v>50</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>207</v>
+        <v>134</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>105</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>248</v>
+        <v>209</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>249</v>
+        <v>134</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>251</v>
+        <v>211</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>105</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>262</v>
+        <v>212</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>263</v>
+        <v>213</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>264</v>
+        <v>210</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>265</v>
+        <v>215</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>105</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>105</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>76</v>
+        <v>315</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>272</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="3">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>105</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:G10"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -5045,7 +5135,6 @@
     <hyperlink ref="F8" r:id="rId7"/>
     <hyperlink ref="F9" r:id="rId8"/>
     <hyperlink ref="F10" r:id="rId9"/>
-    <hyperlink ref="F11" r:id="rId10"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5060,178 +5149,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="B2" s="3">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B3" s="3">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B4" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>197</v>
+        <v>327</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>333</v>
+        <v>201</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>336</v>
+        <v>290</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>278</v>
+        <v>332</v>
       </c>
       <c r="B9" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>283</v>
+        <v>334</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>296</v>
+        <v>336</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B13" s="3">
         <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B16" s="3">
         <v>3</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -5248,13 +5337,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2">
@@ -5262,10 +5351,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3">
@@ -5273,10 +5362,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4">
@@ -5284,10 +5373,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5">
@@ -5295,10 +5384,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6">
@@ -5309,7 +5398,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>
@@ -5327,16 +5416,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2">
@@ -5347,7 +5436,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>312</v>
+        <v>358</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5356,22 +5445,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>312</v>
+        <v>358</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>361</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>312</v>
+        <v>358</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W24.xlsx
+++ b/reports/devops-juniors-israel-2026-W24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="387">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-11T10:56:37</t>
+    <t xml:space="preserve">2026-06-12T10:39:35</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -166,745 +166,838 @@
     <t xml:space="preserve">2026-05-15</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT / Cloud Specialist - 235226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-cloud-specialist-235226-at-experis-israel-4423620429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iFOR FINTECH</t>
   </si>
   <si>
     <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT / Cloud Specialist - 235226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-cloud-specialist-235226-at-experis-israel-4423620429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4423356724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Candex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-candex-4410031859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
   </si>
   <si>
     <t xml:space="preserve">Technical Support Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Fortinet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fortinet-4393535304</t>
+    <t xml:space="preserve">Bria AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-codevalue-4421843930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7988127&amp;gh_jid=7988127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-administrator-at-check-point-software-4427626178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allied Worldwide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qb Systems ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (10156)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bynet Data Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-10156-at-bynet-data-communications-4422796719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-riverside-4409620033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-at-nebius-4425236974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Analyst 11am 8pm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slipstream Life Sciences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pennsylvania, Pennsylvania, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-service-desk-analyst-11am-8pm-slipstream-life-sciences-1133289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux Software Embedded Engineer (Junior position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDA Space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-software-embedded-engineer-junior-position-at-mda-space-4422723139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strategy Analyst Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer IM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (IT Support Specialist)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-it-support-specialist-at-unilink-ltd-4426750419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-extreme-4426743545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intezer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-intezer-4417050672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brazil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GlassesUSA.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-glassesusa-com-4400413150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC &amp; IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-it-support-specialist-at-unilink-ltd-4427557293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beth-El Industries Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4422293340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk - 239819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician - junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excis Compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoham, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-31</t>
   </si>
   <si>
-    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infrastructure &amp; Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Squadron Israel - Hatayeset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-technical-support-specialist-at-the-squadron-israel-hatayeset-4421938671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bria AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist (Part time )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragontail Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-agent-at-dragontail-systems-4422278367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Representative (Full-Time, On-Site | Be’er Sheva – Gav Yam Park)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SITE123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-representative-full-time-on-site-be%E2%80%99er-sheva-%E2%80%93-gav-yam-park-at-site123-4419228442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heyy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-heyy-4423690488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4423670353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-south-apac-sea-anz-ind-subcont-4423614421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-4419979615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
   </si>
   <si>
     <t xml:space="preserve">comblack</t>
   </si>
   <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-comblack-4425486490</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7988127&amp;gh_jid=7988127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allied Worldwide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (10156)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bynet Data Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-10156-at-bynet-data-communications-4422796719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux Software Embedded Engineer (Junior position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MDA Space</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-software-embedded-engineer-junior-position-at-mda-space-4422723139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strategy Analyst Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT Support Technician-Temporary 10 Months</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-support-technician-temporary-10-months-at-augury-4418665913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Eng.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ultra Information Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-eng-at-ultra-information-solutions-4412395476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer IM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-extreme-4426735920</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-extreme-4426743545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (IT Support Specialist)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-it-support-specialist-at-unilink-ltd-4426750419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intezer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-intezer-4417050672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brazil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician - junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excis Compliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoham, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4422293340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk - 239819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist (Part time )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragontail Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-agent-at-dragontail-systems-4422278367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Representative (Full-Time, On-Site | Be’er Sheva – Gav Yam Park)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SITE123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-representative-full-time-on-site-be%E2%80%99er-sheva-%E2%80%93-gav-yam-park-at-site123-4419228442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Service Specialist - Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-service-specialist-tier-1-at-solaredge-technologies-4408365748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-south-apac-sea-anz-ind-subcont-4423614421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-4419979615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-comblack-4427538425</t>
   </si>
   <si>
     <t xml:space="preserve">Information Technology Help Desk</t>
@@ -919,6 +1012,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
   </si>
   <si>
+    <t xml:space="preserve">Technical Support Tier 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yavne, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-at-gness-4426023923</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oktopost</t>
   </si>
   <si>
@@ -931,48 +1036,36 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior Technical Support &amp; Systems Operations Specialist- position no. 1601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBI Investment House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-support-systems-operations-specialist-position-no-1601-at-ibi-investment-house-4423609880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fireberry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fireberry-4415491964</t>
+  </si>
+  <si>
     <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4420118096</t>
   </si>
   <si>
-    <t xml:space="preserve">Fireberry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fireberry-4415491964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-south-apac-sea-anz-ind-subcont-4390170199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unframe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-unframe-4425465742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-4417759260</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Engineering Student</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
   </si>
   <si>
-    <t xml:space="preserve">Programa Trainee 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Universia Argentina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Isidro, San Isidro, Provincia de Buenos Aires, Argentina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-programa-trainee-2026-universia-argentina-1133156</t>
-  </si>
-  <si>
     <t xml:space="preserve">Skill</t>
   </si>
   <si>
@@ -985,9 +1078,6 @@
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
@@ -997,6 +1087,9 @@
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
@@ -1006,22 +1099,22 @@
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
@@ -1036,28 +1129,19 @@
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+    <t xml:space="preserve">Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform/IaC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1215,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7">
@@ -1223,7 +1307,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -1231,7 +1315,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -1239,7 +1323,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -1321,7 +1405,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22">
@@ -1329,7 +1413,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -1337,7 +1421,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1371,7 +1455,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29">
@@ -1399,8 +1483,8 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="33" customWidth="1"/>
-    <col min="4" max="4" width="43" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
@@ -1519,10 +1603,10 @@
         <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>59</v>
@@ -1554,7 +1638,7 @@
         <v>28</v>
       </c>
       <c r="F5" s="3">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>65</v>
@@ -1566,7 +1650,7 @@
         <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -1574,31 +1658,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F6" s="3">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -1630,7 +1714,7 @@
         <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -1638,31 +1722,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9">
@@ -1670,31 +1754,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F9" s="3">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
@@ -1702,13 +1786,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>25</v>
@@ -1717,13 +1801,13 @@
         <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>49</v>
@@ -1734,31 +1818,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>93</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="3">
+        <v>47</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="3">
-        <v>44</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="12">
@@ -1766,31 +1850,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="3">
+        <v>47</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="3">
-        <v>44</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
@@ -1798,31 +1882,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="3">
+        <v>47</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="3">
-        <v>40</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="J13" s="3" t="s">
-        <v>107</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14">
@@ -1830,19 +1914,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>109</v>
@@ -1854,7 +1938,7 @@
         <v>110</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
@@ -1862,19 +1946,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>84</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>114</v>
@@ -1886,7 +1970,7 @@
         <v>115</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>61</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16">
@@ -1894,31 +1978,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>50</v>
+        <v>117</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>61</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17">
@@ -1926,31 +2010,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>46</v>
+        <v>124</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17" s="3">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>122</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
@@ -1958,31 +2042,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>125</v>
+        <v>52</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19">
@@ -1990,31 +2074,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -2022,19 +2106,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F20" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>136</v>
@@ -2046,7 +2130,7 @@
         <v>137</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21">
@@ -2054,31 +2138,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>138</v>
+        <v>88</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="3">
+        <v>30</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="3">
-        <v>27</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="22">
@@ -2086,31 +2170,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="E22" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>145</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>146</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>49</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23">
@@ -2121,28 +2205,28 @@
         <v>147</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>135</v>
+        <v>52</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24">
@@ -2150,31 +2234,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>99</v>
+        <v>153</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F24" s="3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>153</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25">
@@ -2182,31 +2266,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>67</v>
+        <v>156</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26">
@@ -2214,28 +2298,28 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>49</v>
@@ -2278,7 +2362,7 @@
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2291,7 +2375,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>36</v>
@@ -2306,22 +2390,22 @@
         <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2">
@@ -2344,7 +2428,7 @@
         <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2356,7 +2440,7 @@
         <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -2379,7 +2463,7 @@
         <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2391,7 +2475,7 @@
         <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2405,16 +2489,16 @@
         <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2426,7 +2510,7 @@
         <v>61</v>
       </c>
       <c r="K4" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -2443,13 +2527,13 @@
         <v>28</v>
       </c>
       <c r="E5" s="3">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
@@ -2458,45 +2542,45 @@
         <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="K5" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E6" s="3">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="K6" s="3">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -2519,7 +2603,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
@@ -2528,91 +2612,91 @@
         <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="K7" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="K8" s="3">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E9" s="3">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="K9" s="3">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>25</v>
@@ -2621,150 +2705,150 @@
         <v>47</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>49</v>
       </c>
       <c r="K10" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>93</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="3">
+        <v>47</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="3">
-        <v>44</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="K11" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="3">
+        <v>47</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="3">
-        <v>44</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K12" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="3">
+        <v>47</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="3">
-        <v>40</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="J13" s="3" t="s">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="K13" s="3">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>109</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
@@ -2773,33 +2857,33 @@
         <v>110</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="K14" s="3">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>84</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>114</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
@@ -2808,173 +2892,173 @@
         <v>115</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>50</v>
+        <v>117</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>61</v>
+        <v>121</v>
       </c>
       <c r="K16" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>46</v>
+        <v>124</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E17" s="3">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>122</v>
+        <v>61</v>
       </c>
       <c r="K17" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>125</v>
+        <v>52</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="K18" s="3">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="K19" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E20" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>136</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
@@ -2983,80 +3067,80 @@
         <v>137</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="K20" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>138</v>
+        <v>88</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="3">
+        <v>30</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="3">
-        <v>27</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="K21" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="D22" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>145</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>146</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>49</v>
+        <v>141</v>
       </c>
       <c r="K22" s="3">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -3064,162 +3148,162 @@
         <v>147</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>135</v>
+        <v>52</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K23" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>99</v>
+        <v>153</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E24" s="3">
+        <v>28</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K24" s="3">
         <v>23</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="K24" s="3">
-        <v>16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>67</v>
+        <v>156</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="K25" s="3">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>49</v>
       </c>
       <c r="K26" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>170</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
@@ -3231,7 +3315,7 @@
         <v>172</v>
       </c>
       <c r="K27" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
@@ -3245,28 +3329,28 @@
         <v>175</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>176</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>177</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>172</v>
+        <v>49</v>
       </c>
       <c r="K28" s="3">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29">
@@ -3277,252 +3361,252 @@
         <v>179</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" s="3">
+        <v>20</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29" s="3">
-        <v>17</v>
-      </c>
-      <c r="F29" s="3" t="s">
+      <c r="G29" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" s="3" t="s">
+      <c r="J29" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>183</v>
-      </c>
       <c r="K29" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="3">
+        <v>20</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="G30" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E30" s="3">
-        <v>17</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>187</v>
-      </c>
       <c r="J30" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="K30" s="3">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="D31" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="3">
+        <v>20</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="G31" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="3">
-        <v>17</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>192</v>
-      </c>
       <c r="J31" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K31" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="D32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="3">
+        <v>20</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E32" s="3">
-        <v>16</v>
-      </c>
-      <c r="F32" s="3" t="s">
+      <c r="G32" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="J32" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K32" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>50</v>
+        <v>196</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>135</v>
+        <v>198</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E33" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>61</v>
+        <v>182</v>
       </c>
       <c r="K33" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E34" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>55</v>
+        <v>206</v>
       </c>
       <c r="K34" s="3">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>74</v>
+        <v>198</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E35" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>205</v>
+        <v>49</v>
       </c>
       <c r="K35" s="3">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>27</v>
@@ -3531,103 +3615,103 @@
         <v>13</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>208</v>
+        <v>77</v>
       </c>
       <c r="K36" s="3">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>134</v>
+        <v>212</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E37" s="3">
         <v>13</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K37" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="C38" s="3" t="s">
-        <v>214</v>
+        <v>74</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E38" s="3">
         <v>13</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>61</v>
+        <v>220</v>
       </c>
       <c r="K38" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
@@ -3636,33 +3720,33 @@
         <v>13</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="K39" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
@@ -3671,33 +3755,33 @@
         <v>13</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="K40" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>82</v>
+        <v>229</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>99</v>
+        <v>231</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
@@ -3706,22 +3790,22 @@
         <v>13</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>195</v>
+        <v>232</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="K41" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -3729,115 +3813,115 @@
         <v>225</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>226</v>
+        <v>152</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>214</v>
+        <v>113</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E42" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>228</v>
+        <v>67</v>
       </c>
       <c r="K42" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>231</v>
+        <v>108</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>55</v>
+        <v>116</v>
       </c>
       <c r="K43" s="3">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E44" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="K44" s="3">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>77</v>
+        <v>240</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>64</v>
+        <v>242</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
@@ -3846,135 +3930,135 @@
         <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="K45" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>209</v>
+        <v>117</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="K46" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>245</v>
+        <v>52</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E47" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>248</v>
+        <v>217</v>
       </c>
       <c r="K47" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>144</v>
+        <v>251</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>135</v>
+        <v>52</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E48" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="K48" s="3">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>64</v>
@@ -3983,71 +4067,71 @@
         <v>25</v>
       </c>
       <c r="E49" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="K49" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>144</v>
+        <v>257</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>135</v>
+        <v>258</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E50" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>208</v>
+        <v>77</v>
       </c>
       <c r="K50" s="3">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>258</v>
+        <v>160</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>259</v>
+        <v>153</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
@@ -4056,33 +4140,33 @@
         <v>6</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="K51" s="3">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>240</v>
+        <v>266</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
@@ -4091,33 +4175,33 @@
         <v>6</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="K52" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
@@ -4126,33 +4210,33 @@
         <v>6</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="K53" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>64</v>
+        <v>274</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
@@ -4161,33 +4245,33 @@
         <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>241</v>
+        <v>275</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>111</v>
+        <v>277</v>
       </c>
       <c r="K54" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>25</v>
@@ -4196,33 +4280,33 @@
         <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>172</v>
+        <v>217</v>
       </c>
       <c r="K55" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
@@ -4231,33 +4315,33 @@
         <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>278</v>
+        <v>77</v>
       </c>
       <c r="K56" s="3">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
@@ -4266,80 +4350,80 @@
         <v>6</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>153</v>
+        <v>288</v>
       </c>
       <c r="K57" s="3">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>282</v>
+        <v>235</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>283</v>
+        <v>160</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>284</v>
+        <v>153</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E58" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>287</v>
+        <v>83</v>
       </c>
       <c r="K58" s="3">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>288</v>
+        <v>225</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>190</v>
+        <v>266</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E59" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>290</v>
+        <v>262</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>31</v>
@@ -4348,336 +4432,336 @@
         <v>291</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="K59" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E60" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>61</v>
+        <v>121</v>
       </c>
       <c r="K60" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E61" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>287</v>
+        <v>182</v>
       </c>
       <c r="K61" s="3">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>44</v>
+        <v>299</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E62" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>55</v>
+        <v>303</v>
       </c>
       <c r="K62" s="3">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E63" s="3">
+        <v>6</v>
+      </c>
+      <c r="F63" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E63" s="3">
-        <v>3</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>299</v>
-      </c>
       <c r="G63" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="K63" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>128</v>
+        <v>306</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>84</v>
+        <v>308</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E64" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>122</v>
+        <v>311</v>
       </c>
       <c r="K64" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>67</v>
+        <v>312</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>64</v>
+        <v>314</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E65" s="3">
+        <v>4</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="K65" s="3">
         <v>3</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K65" s="3">
-        <v>18</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>82</v>
+        <v>317</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E66" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>285</v>
+        <v>319</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>183</v>
+        <v>55</v>
       </c>
       <c r="K66" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E67" s="3">
+        <v>4</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="J67" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E67" s="3">
-        <v>3</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="K67" s="3">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>44</v>
+        <v>306</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>292</v>
+        <v>323</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E68" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="K68" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>64</v>
+        <v>308</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>25</v>
@@ -4686,33 +4770,33 @@
         <v>3</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="K69" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>44</v>
+        <v>261</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>294</v>
+        <v>326</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>64</v>
+        <v>153</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>25</v>
@@ -4721,92 +4805,304 @@
         <v>3</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="K70" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>199</v>
+        <v>329</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E71" s="3">
-        <v>0</v>
-      </c>
-      <c r="F71" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>330</v>
+      </c>
       <c r="G71" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="K71" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="K72" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E73" s="3">
+        <v>3</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="K73" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E74" s="3">
+        <v>3</v>
+      </c>
+      <c r="F74" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="D72" s="3" t="s">
+      <c r="G74" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K74" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E75" s="3">
+        <v>3</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K76" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E77" s="3">
+        <v>3</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K77" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E78" s="3">
         <v>0</v>
       </c>
-      <c r="F72" s="3"/>
-      <c r="G72" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="K72" s="3">
-        <v>0</v>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="K78" s="3">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K72"/>
+  <autoFilter ref="A1:K78"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4879,6 +5175,12 @@
     <hyperlink ref="I70" r:id="rId69"/>
     <hyperlink ref="I71" r:id="rId70"/>
     <hyperlink ref="I72" r:id="rId71"/>
+    <hyperlink ref="I73" r:id="rId72"/>
+    <hyperlink ref="I74" r:id="rId73"/>
+    <hyperlink ref="I75" r:id="rId74"/>
+    <hyperlink ref="I76" r:id="rId75"/>
+    <hyperlink ref="I77" r:id="rId76"/>
+    <hyperlink ref="I78" r:id="rId77"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4886,9 +5188,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="53" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -4909,10 +5211,10 @@
         <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>43</v>
@@ -4920,171 +5222,171 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>50</v>
+        <v>186</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>116</v>
+        <v>187</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>118</v>
+        <v>189</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>119</v>
+        <v>190</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>50</v>
+        <v>191</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>209</v>
+        <v>254</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>210</v>
+        <v>249</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>211</v>
+        <v>255</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>212</v>
+        <v>117</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>213</v>
+        <v>304</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>210</v>
+        <v>297</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>215</v>
+        <v>305</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>282</v>
+        <v>317</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>292</v>
+        <v>318</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>26</v>
@@ -5093,38 +5395,63 @@
         <v>4</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>285</v>
+        <v>319</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>293</v>
+        <v>320</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>315</v>
+        <v>261</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>309</v>
+      </c>
       <c r="F10" s="3" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="3">
+        <v>3</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G11"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -5135,6 +5462,7 @@
     <hyperlink ref="F8" r:id="rId7"/>
     <hyperlink ref="F9" r:id="rId8"/>
     <hyperlink ref="F10" r:id="rId9"/>
+    <hyperlink ref="F11" r:id="rId10"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5149,178 +5477,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>321</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="B2" s="3">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>322</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B3" s="3">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>326</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>328</v>
+        <v>357</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>201</v>
+        <v>358</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>329</v>
+        <v>359</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>299</v>
+        <v>213</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>330</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B8" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>331</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="B9" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>335</v>
+        <v>364</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>336</v>
+        <v>365</v>
       </c>
       <c r="B11" s="3">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>337</v>
+        <v>366</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>338</v>
+        <v>367</v>
       </c>
       <c r="B12" s="3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>339</v>
+        <v>368</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>340</v>
+        <v>369</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>341</v>
+        <v>370</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>343</v>
+        <v>368</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>344</v>
+        <v>372</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>345</v>
+        <v>373</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>346</v>
+        <v>374</v>
       </c>
       <c r="B16" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>347</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -5340,10 +5668,10 @@
         <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>348</v>
+        <v>376</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>349</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2">
@@ -5351,10 +5679,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3">
@@ -5362,10 +5690,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>351</v>
+        <v>379</v>
       </c>
     </row>
     <row r="4">
@@ -5373,10 +5701,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>352</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5">
@@ -5387,7 +5715,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>353</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6">
@@ -5398,7 +5726,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>354</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -5419,13 +5747,13 @@
         <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>355</v>
+        <v>383</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>356</v>
+        <v>384</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>357</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2">
@@ -5436,7 +5764,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>358</v>
+        <v>386</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5445,10 +5773,10 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>358</v>
+        <v>386</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -5460,7 +5788,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>358</v>
+        <v>386</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W24.xlsx
+++ b/reports/devops-juniors-israel-2026-W24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="376">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-12T10:39:35</t>
+    <t xml:space="preserve">2026-06-14T09:54:07</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -166,774 +166,747 @@
     <t xml:space="preserve">2026-05-15</t>
   </si>
   <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC &amp; Linux Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-linux-systems-engineer-at-ben-gurion-university-of-the-negev-4427607653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT / Cloud Specialist - 235226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-cloud-specialist-235226-at-experis-israel-4423620429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4408743594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4423356724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bria AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Product Operations – Part-Time Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-product-operations-%E2%80%93-part-time-student-at-finout-4427681349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-administrator-at-check-point-software-4427626178</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-12</t>
   </si>
   <si>
-    <t xml:space="preserve">‫System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT / Cloud Specialist - 235226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-cloud-specialist-235226-at-experis-israel-4423620429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iFOR FINTECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zensar Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allied Worldwide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-03</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4423356724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Candex</t>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Operations Engineer (36602)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-operations-engineer-36602-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4427531206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qb Systems ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (10156)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bynet Data Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-10156-at-bynet-data-communications-4422796719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk &amp; IT Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-it-administrator-at-mize-4425999700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-riverside-4409620033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux Software Embedded Engineer (Junior position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDA Space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-software-embedded-engineer-junior-position-at-mda-space-4422723139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strategy Analyst Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-extreme-4426735920</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (IT Support Specialist)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-it-support-specialist-at-unilink-ltd-4426750419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-extreme-4426743545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plarium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-administrator-at-plarium-4402847792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intezer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-intezer-4417050672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brazil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GlassesUSA.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-glassesusa-com-4400413150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4425818718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4422293340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk - 239819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician - junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
   </si>
   <si>
     <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-candex-4410031859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bria AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-codevalue-4421843930</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7988127&amp;gh_jid=7988127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7988656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-administrator-at-check-point-software-4427626178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allied Worldwide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (10156)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bynet Data Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-10156-at-bynet-data-communications-4422796719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-riverside-4409620033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-at-nebius-4425236974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Analyst 11am 8pm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slipstream Life Sciences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pennsylvania, Pennsylvania, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-service-desk-analyst-11am-8pm-slipstream-life-sciences-1133289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux Software Embedded Engineer (Junior position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MDA Space</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-software-embedded-engineer-junior-position-at-mda-space-4422723139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strategy Analyst Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer IM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (IT Support Specialist)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-it-support-specialist-at-unilink-ltd-4426750419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-extreme-4426743545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intezer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-intezer-4417050672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brazil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GlassesUSA.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-glassesusa-com-4400413150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC &amp; IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-it-support-specialist-at-unilink-ltd-4427557293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beth-El Industries Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragontail Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-agent-at-dragontail-systems-4422278367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zoho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-zoho-4427961067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heyy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-heyy-4423690488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Representative (Full-Time, On-Site | Be’er Sheva – Gav Yam Park)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SITE123</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-sqlink-group-4422293340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk - 239819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician - junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excis Compliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoham, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist (Part time )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragontail Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-agent-at-dragontail-systems-4422278367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Representative (Full-Time, On-Site | Be’er Sheva – Gav Yam Park)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SITE123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-representative-full-time-on-site-be%E2%80%99er-sheva-%E2%80%93-gav-yam-park-at-site123-4419228442</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Heyy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-heyy-4423690488</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Operations Specialist</t>
   </si>
   <si>
@@ -949,90 +922,78 @@
     <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
+    <t xml:space="preserve">NOC Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4423670353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-south-apac-sea-anz-ind-subcont-4423614421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-comblack-4427538425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-at-comblack-4427544458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Tier 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yavne, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-at-gness-4426023923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4425470752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
   </si>
   <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4423670353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-south-apac-sea-anz-ind-subcont-4423614421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-4419979615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-comblack-4427538425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Tier 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yavne, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-at-gness-4426023923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4425470752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
   </si>
   <si>
@@ -1042,28 +1003,31 @@
     <t xml:space="preserve">IBI Investment House</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-support-systems-operations-specialist-position-no-1601-at-ibi-investment-house-4423609880</t>
   </si>
   <si>
+    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4420118096</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fireberry</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fireberry-4415491964</t>
   </si>
   <si>
-    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4420118096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
+    <t xml:space="preserve">Especialista de Soporte Service Desk Remoto Horario rotativo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canvia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lima, Lima, PerÃº</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-especialista-de-soporte-service-desk-remoto-horario-rotativo-canvia-1133349</t>
   </si>
   <si>
     <t xml:space="preserve">Skill</t>
@@ -1087,30 +1051,30 @@
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
     <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
@@ -1129,19 +1093,22 @@
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1299,7 +1266,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1307,7 +1274,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1315,7 +1282,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -1323,7 +1290,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>246</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -1405,7 +1372,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22">
@@ -1413,7 +1380,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
@@ -1421,7 +1388,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -1455,7 +1422,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29">
@@ -1463,7 +1430,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
@@ -1483,7 +1450,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1606,7 +1573,7 @@
         <v>26</v>
       </c>
       <c r="F4" s="3">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>59</v>
@@ -1664,25 +1631,25 @@
         <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
@@ -1690,31 +1657,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
@@ -1728,25 +1695,25 @@
         <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="3">
+        <v>57</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="3">
-        <v>52</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -1754,31 +1721,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="3">
+        <v>52</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="3">
-        <v>51</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">
@@ -1786,31 +1753,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="3">
+        <v>51</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="3">
-        <v>47</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="11">
@@ -1818,13 +1785,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>25</v>
@@ -1833,16 +1800,16 @@
         <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>95</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
@@ -1850,13 +1817,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="D12" s="3" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>25</v>
@@ -1865,16 +1832,16 @@
         <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -1882,13 +1849,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>25</v>
@@ -1897,13 +1864,13 @@
         <v>47</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>49</v>
@@ -1914,13 +1881,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
@@ -1929,16 +1896,16 @@
         <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -1946,31 +1913,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1978,13 +1945,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
@@ -1993,16 +1960,16 @@
         <v>40</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17">
@@ -2010,13 +1977,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>26</v>
@@ -2025,16 +1992,16 @@
         <v>36</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -2042,31 +2009,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F18" s="3">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -2074,31 +2041,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3">
+        <v>30</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="I19" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20">
@@ -2106,31 +2073,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21">
@@ -2138,13 +2105,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>88</v>
+        <v>135</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
@@ -2153,16 +2120,16 @@
         <v>30</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="22">
@@ -2170,31 +2137,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="E22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="3">
+        <v>28</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="3">
-        <v>30</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="23">
@@ -2202,19 +2169,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>149</v>
@@ -2226,7 +2193,7 @@
         <v>150</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>55</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24">
@@ -2240,25 +2207,25 @@
         <v>152</v>
       </c>
       <c r="D24" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="3">
+        <v>27</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F24" s="3">
-        <v>28</v>
-      </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="25">
@@ -2272,13 +2239,13 @@
         <v>157</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F25" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>158</v>
@@ -2290,7 +2257,7 @@
         <v>159</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26">
@@ -2298,13 +2265,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>127</v>
+        <v>160</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>26</v>
@@ -2313,16 +2280,16 @@
         <v>24</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -2362,7 +2329,7 @@
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2375,7 +2342,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>36</v>
@@ -2390,22 +2357,22 @@
         <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2">
@@ -2428,7 +2395,7 @@
         <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2440,7 +2407,7 @@
         <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -2463,7 +2430,7 @@
         <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2475,7 +2442,7 @@
         <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -2492,13 +2459,13 @@
         <v>26</v>
       </c>
       <c r="E4" s="3">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2510,7 +2477,7 @@
         <v>61</v>
       </c>
       <c r="K4" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2533,7 +2500,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
@@ -2545,7 +2512,7 @@
         <v>67</v>
       </c>
       <c r="K5" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2556,66 +2523,66 @@
         <v>69</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="K6" s="3">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="K7" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2626,112 +2593,112 @@
         <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="3">
+        <v>57</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="3">
-        <v>52</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="K8" s="3">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="D9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="3">
+        <v>52</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="3">
-        <v>51</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="K9" s="3">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="3">
+        <v>51</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="3">
-        <v>47</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="K10" s="3">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>25</v>
@@ -2740,33 +2707,33 @@
         <v>47</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="K11" s="3">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="C12" s="3" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>25</v>
@@ -2775,33 +2742,33 @@
         <v>47</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="K12" s="3">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>25</v>
@@ -2810,33 +2777,33 @@
         <v>47</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>49</v>
       </c>
       <c r="K13" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
@@ -2845,68 +2812,68 @@
         <v>44</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="K14" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="K15" s="3">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>25</v>
@@ -2915,33 +2882,33 @@
         <v>40</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="K16" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>26</v>
@@ -2950,138 +2917,138 @@
         <v>36</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="K17" s="3">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E18" s="3">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="K18" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3">
+        <v>30</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="I19" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="K19" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="K20" s="3">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>88</v>
+        <v>135</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
@@ -3090,80 +3057,80 @@
         <v>30</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="K21" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="D22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="3">
+        <v>28</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="3">
-        <v>30</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="K22" s="3">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>149</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
@@ -3172,10 +3139,10 @@
         <v>150</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>55</v>
+        <v>134</v>
       </c>
       <c r="K23" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -3186,31 +3153,31 @@
         <v>152</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="3">
+        <v>27</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="3">
-        <v>28</v>
-      </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="K24" s="3">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
@@ -3221,19 +3188,19 @@
         <v>157</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E25" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>158</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
@@ -3242,21 +3209,21 @@
         <v>159</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="K25" s="3">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>127</v>
+        <v>160</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>26</v>
@@ -3265,45 +3232,45 @@
         <v>24</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="K26" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>170</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
@@ -3312,115 +3279,115 @@
         <v>171</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>172</v>
+        <v>49</v>
       </c>
       <c r="K27" s="3">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" s="3">
+        <v>23</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="G28" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="J28" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="3">
-        <v>20</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="K28" s="3">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="D29" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3">
         <v>20</v>
       </c>
       <c r="F29" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="J29" s="3" t="s">
-        <v>182</v>
+        <v>49</v>
       </c>
       <c r="K29" s="3">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>88</v>
+        <v>181</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>52</v>
+        <v>142</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E30" s="3">
         <v>20</v>
       </c>
       <c r="F30" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I30" s="3" t="s">
+      <c r="J30" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="J30" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="K30" s="3">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -3431,7 +3398,7 @@
         <v>187</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>188</v>
+        <v>70</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
@@ -3440,33 +3407,33 @@
         <v>20</v>
       </c>
       <c r="F31" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="J31" s="3" t="s">
-        <v>55</v>
+        <v>185</v>
       </c>
       <c r="K31" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>191</v>
+        <v>68</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>193</v>
+        <v>70</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
@@ -3475,33 +3442,33 @@
         <v>20</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="K32" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>29</v>
@@ -3510,33 +3477,33 @@
         <v>18</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K33" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>27</v>
@@ -3545,33 +3512,33 @@
         <v>17</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="K34" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>207</v>
+        <v>50</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>208</v>
+        <v>141</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>26</v>
@@ -3580,33 +3547,33 @@
         <v>16</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="K35" s="3">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>27</v>
@@ -3615,103 +3582,103 @@
         <v>13</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>77</v>
+        <v>209</v>
       </c>
       <c r="K36" s="3">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E37" s="3">
         <v>13</v>
       </c>
       <c r="F37" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>216</v>
-      </c>
       <c r="J37" s="3" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="K37" s="3">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E38" s="3">
         <v>13</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K38" s="3">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
@@ -3720,33 +3687,33 @@
         <v>13</v>
       </c>
       <c r="F39" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>224</v>
-      </c>
       <c r="J39" s="3" t="s">
-        <v>182</v>
+        <v>67</v>
       </c>
       <c r="K39" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>226</v>
+        <v>141</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>80</v>
+        <v>224</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
@@ -3755,33 +3722,33 @@
         <v>13</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>217</v>
+        <v>67</v>
       </c>
       <c r="K40" s="3">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>231</v>
+        <v>52</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
@@ -3790,33 +3757,33 @@
         <v>13</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="K41" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>152</v>
+        <v>231</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
@@ -3828,100 +3795,100 @@
         <v>232</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>67</v>
+        <v>145</v>
       </c>
       <c r="K42" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="K43" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E44" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="K44" s="3">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
@@ -3930,33 +3897,33 @@
         <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>77</v>
+        <v>246</v>
       </c>
       <c r="K45" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>245</v>
+        <v>70</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
@@ -3965,33 +3932,33 @@
         <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="K46" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
@@ -4000,33 +3967,33 @@
         <v>10</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K47" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>88</v>
+        <v>253</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>52</v>
+        <v>255</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
@@ -4035,103 +4002,103 @@
         <v>10</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="K48" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>222</v>
+        <v>157</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>64</v>
+        <v>142</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E49" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>55</v>
+        <v>209</v>
       </c>
       <c r="K49" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>77</v>
+        <v>185</v>
       </c>
       <c r="K50" s="3">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>153</v>
+        <v>266</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
@@ -4140,33 +4107,33 @@
         <v>6</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>220</v>
+        <v>175</v>
       </c>
       <c r="K51" s="3">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
@@ -4175,33 +4142,33 @@
         <v>6</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>182</v>
+        <v>273</v>
       </c>
       <c r="K52" s="3">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>63</v>
+        <v>275</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>270</v>
+        <v>70</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
@@ -4210,33 +4177,33 @@
         <v>6</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
       <c r="K53" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>272</v>
+        <v>214</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
@@ -4245,33 +4212,33 @@
         <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>277</v>
+        <v>55</v>
       </c>
       <c r="K54" s="3">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>52</v>
+        <v>281</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>25</v>
@@ -4280,33 +4247,33 @@
         <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>217</v>
+        <v>134</v>
       </c>
       <c r="K55" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>281</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>283</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
@@ -4315,33 +4282,33 @@
         <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>77</v>
+        <v>185</v>
       </c>
       <c r="K56" s="3">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>285</v>
+        <v>111</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
@@ -4350,33 +4317,33 @@
         <v>6</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>288</v>
+        <v>61</v>
       </c>
       <c r="K57" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>235</v>
+        <v>111</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>160</v>
+        <v>290</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>153</v>
+        <v>109</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>25</v>
@@ -4385,33 +4352,33 @@
         <v>6</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>259</v>
+        <v>285</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="K58" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>225</v>
+        <v>292</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>266</v>
+        <v>58</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>25</v>
@@ -4420,89 +4387,89 @@
         <v>6</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>77</v>
+        <v>296</v>
       </c>
       <c r="K59" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>52</v>
+        <v>299</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E60" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>262</v>
+        <v>300</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>121</v>
+        <v>246</v>
       </c>
       <c r="K60" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E61" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>182</v>
+        <v>139</v>
       </c>
       <c r="K61" s="3">
         <v>2</v>
@@ -4510,174 +4477,174 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B62" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E62" s="3">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E62" s="3">
-        <v>6</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>259</v>
-      </c>
       <c r="G62" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>303</v>
+        <v>67</v>
       </c>
       <c r="K62" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>108</v>
+        <v>299</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E63" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="J63" s="3" t="s">
         <v>55</v>
       </c>
       <c r="K63" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>306</v>
+        <v>257</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>308</v>
+        <v>142</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E64" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>310</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>311</v>
+        <v>139</v>
       </c>
       <c r="K64" s="3">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="C65" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E65" s="3">
+        <v>3</v>
+      </c>
+      <c r="F65" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="G65" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I65" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E65" s="3">
-        <v>4</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>316</v>
-      </c>
       <c r="J65" s="3" t="s">
-        <v>141</v>
+        <v>218</v>
       </c>
       <c r="K65" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I66" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E66" s="3">
-        <v>4</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>320</v>
-      </c>
       <c r="J66" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="K66" s="3">
         <v>0</v>
@@ -4685,83 +4652,83 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E67" s="3">
+        <v>3</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I67" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E67" s="3">
+      <c r="J67" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="K67" s="3">
         <v>4</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="K67" s="3">
-        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>306</v>
+        <v>87</v>
       </c>
       <c r="B68" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E68" s="3">
+        <v>3</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I68" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="C68" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E68" s="3">
-        <v>4</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>324</v>
-      </c>
       <c r="J68" s="3" t="s">
-        <v>311</v>
+        <v>129</v>
       </c>
       <c r="K68" s="3">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>44</v>
+        <v>111</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>308</v>
+        <v>70</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>25</v>
@@ -4770,33 +4737,33 @@
         <v>3</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="K69" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>261</v>
+        <v>327</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>153</v>
+        <v>109</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>25</v>
@@ -4805,33 +4772,33 @@
         <v>3</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>55</v>
+        <v>139</v>
       </c>
       <c r="K70" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>328</v>
+        <v>230</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>25</v>
@@ -4840,10 +4807,10 @@
         <v>3</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>31</v>
@@ -4852,21 +4819,21 @@
         <v>331</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="K71" s="3">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>333</v>
-      </c>
       <c r="C72" s="3" t="s">
-        <v>334</v>
+        <v>109</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>25</v>
@@ -4875,33 +4842,33 @@
         <v>3</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>182</v>
+        <v>55</v>
       </c>
       <c r="K72" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>84</v>
+        <v>334</v>
       </c>
       <c r="B73" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>336</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>25</v>
@@ -4910,199 +4877,26 @@
         <v>3</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>337</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="K73" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E74" s="3">
-        <v>3</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="J74" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="K74" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E75" s="3">
-        <v>3</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="J75" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K75" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E76" s="3">
-        <v>3</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="K76" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E77" s="3">
-        <v>3</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="J77" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="K77" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E78" s="3">
-        <v>0</v>
-      </c>
-      <c r="F78" s="3"/>
-      <c r="G78" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="J78" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="K78" s="3">
-        <v>18</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K78"/>
+  <autoFilter ref="A1:K73"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -5176,11 +4970,6 @@
     <hyperlink ref="I71" r:id="rId70"/>
     <hyperlink ref="I72" r:id="rId71"/>
     <hyperlink ref="I73" r:id="rId72"/>
-    <hyperlink ref="I74" r:id="rId73"/>
-    <hyperlink ref="I75" r:id="rId74"/>
-    <hyperlink ref="I76" r:id="rId75"/>
-    <hyperlink ref="I77" r:id="rId76"/>
-    <hyperlink ref="I78" r:id="rId77"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5189,8 +4978,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -5211,10 +5000,10 @@
         <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>43</v>
@@ -5222,125 +5011,125 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>149</v>
+        <v>105</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>150</v>
+        <v>106</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>186</v>
+        <v>120</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>187</v>
+        <v>121</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D5" s="3">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>189</v>
+        <v>122</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>190</v>
+        <v>123</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>254</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
@@ -5349,21 +5138,21 @@
         <v>10</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
@@ -5372,44 +5161,44 @@
         <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="3">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>320</v>
-      </c>
       <c r="G9" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>261</v>
+        <v>334</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>25</v>
@@ -5418,40 +5207,17 @@
         <v>3</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="3">
-        <v>3</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:G10"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -5462,7 +5228,6 @@
     <hyperlink ref="F8" r:id="rId7"/>
     <hyperlink ref="F9" r:id="rId8"/>
     <hyperlink ref="F10" r:id="rId9"/>
-    <hyperlink ref="F11" r:id="rId10"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5477,178 +5242,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="B2" s="3">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="B3" s="3">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="B4" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>358</v>
+        <v>325</v>
       </c>
       <c r="B6" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>213</v>
+        <v>348</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B8" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>342</v>
+        <v>207</v>
       </c>
       <c r="B9" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>363</v>
+        <v>316</v>
       </c>
       <c r="B10" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="B11" s="3">
         <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -5668,10 +5433,10 @@
         <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2">
@@ -5679,10 +5444,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3">
@@ -5690,10 +5455,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4">
@@ -5701,10 +5466,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5">
@@ -5715,7 +5480,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
     </row>
     <row r="6">
@@ -5726,7 +5491,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -5747,13 +5512,13 @@
         <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2">
@@ -5761,10 +5526,10 @@
         <v>32</v>
       </c>
       <c r="B2" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5773,10 +5538,10 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -5788,7 +5553,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="D4" s="3"/>
     </row>
